--- a/output/HS_Code_Summary_MOREK_CZ_CZ26008741.xlsx
+++ b/output/HS_Code_Summary_MOREK_CZ_CZ26008741.xlsx
@@ -621,20 +621,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -789,45 +790,50 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
+          <t>Faktura / Invoice (hodnota USD)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
           <t>Popis zboží (CZ)</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Description (EN)</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Čistá hm. / Net (kg)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Hrubá hm. / Gross (kg)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Množství / Qty</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>MJ / Unit</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Celní hodnota / Customs value (USD)</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>CBAM</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Antidumping</t>
         </is>
@@ -846,41 +852,47 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
+          <t>CI-26051504: 22 100,66
+CI-26051902: 376,69</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
           <t>Smršťovací trubice silnostěnná a středněstěnná — Izolace, ochrana a vnější těsnění pro kabely níz. a stř. napětí</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Heat-shrink tubing, heavywall and mediumwall (with and without adhesive liner) — insulation, protection and outer sealing for LV/MV cables</t>
         </is>
       </c>
-      <c r="E16" s="7">
+      <c r="F16" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$I$10:$I$18,'Rozpad-dle-produktu'!$C$10:$C$18,"HW")+SUMIFS('Rozpad-dle-produktu'!$I$10:$I$18,'Rozpad-dle-produktu'!$C$10:$C$18,"MW-A")+SUMIFS('Rozpad-dle-produktu'!$I$10:$I$18,'Rozpad-dle-produktu'!$C$10:$C$18,"MW-U")</f>
         <v>2978.58</v>
       </c>
-      <c r="F16" s="7">
+      <c r="G16" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$J$10:$J$18,'Rozpad-dle-produktu'!$C$10:$C$18,"HW")+SUMIFS('Rozpad-dle-produktu'!$J$10:$J$18,'Rozpad-dle-produktu'!$C$10:$C$18,"MW-A")+SUMIFS('Rozpad-dle-produktu'!$J$10:$J$18,'Rozpad-dle-produktu'!$C$10:$C$18,"MW-U")</f>
         <v>3452.37</v>
       </c>
-      <c r="G16" s="8">
+      <c r="H16" s="8">
         <f>SUMIFS('Rozpad-dle-produktu'!$G$10:$G$18,'Rozpad-dle-produktu'!$C$10:$C$18,"HW")+SUMIFS('Rozpad-dle-produktu'!$G$10:$G$18,'Rozpad-dle-produktu'!$C$10:$C$18,"MW-A")+SUMIFS('Rozpad-dle-produktu'!$G$10:$G$18,'Rozpad-dle-produktu'!$C$10:$C$18,"MW-U")</f>
         <v>28935.0</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>ks / pcs</t>
         </is>
       </c>
-      <c r="I16" s="7">
+      <c r="J16" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$K$10:$K$18,'Rozpad-dle-produktu'!$C$10:$C$18,"HW")+SUMIFS('Rozpad-dle-produktu'!$K$10:$K$18,'Rozpad-dle-produktu'!$C$10:$C$18,"MW-A")+SUMIFS('Rozpad-dle-produktu'!$K$10:$K$18,'Rozpad-dle-produktu'!$C$10:$C$18,"MW-U")</f>
         <v>22477.35</v>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>Ne / No</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>Ne / No — žádné opatření nezjištěno</t>
         </is>
@@ -899,41 +911,47 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t>CI-26051504: 6 347,52
+CI-26051902: 17 612,08</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
           <t>Spojovací set — Izolace a ochrana pro kabely nízkého napětí</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>MSTS cable jointing/termination kits — insulation and protection for LV cables</t>
         </is>
       </c>
-      <c r="E17" s="7">
+      <c r="F17" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$I$10:$I$18,'Rozpad-dle-produktu'!$C$10:$C$18,"KIT")</f>
         <v>4488.82</v>
       </c>
-      <c r="F17" s="7">
+      <c r="G17" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$J$10:$J$18,'Rozpad-dle-produktu'!$C$10:$C$18,"KIT")</f>
         <v>5415.63</v>
       </c>
-      <c r="G17" s="8">
+      <c r="H17" s="8">
         <f>SUMIFS('Rozpad-dle-produktu'!$G$10:$G$18,'Rozpad-dle-produktu'!$C$10:$C$18,"KIT")</f>
         <v>9530.0</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>sada / kit</t>
         </is>
       </c>
-      <c r="I17" s="7">
+      <c r="J17" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$K$10:$K$18,'Rozpad-dle-produktu'!$C$10:$C$18,"KIT")</f>
         <v>23959.6</v>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>Ne / No</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>Ne / No — žádné opatření nezjištěno</t>
         </is>
@@ -952,41 +970,47 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
+          <t>CI-26051504: 14 385,43
+CI-26051902: 6 120,94</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
           <t>Smršťovací bužírka tenkostěnná — Izolace a ochrana pro kabely nízkého napětí</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Thinwall heat-shrink sleeving 2:1 — insulation and protection for LV cables</t>
         </is>
       </c>
-      <c r="E18" s="7">
+      <c r="F18" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$I$10:$I$18,'Rozpad-dle-produktu'!$C$10:$C$18,"TW")</f>
         <v>2175.6</v>
       </c>
-      <c r="F18" s="7">
+      <c r="G18" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$J$10:$J$18,'Rozpad-dle-produktu'!$C$10:$C$18,"TW")</f>
         <v>2562.0</v>
       </c>
-      <c r="G18" s="8">
+      <c r="H18" s="8">
         <f>SUMIFS('Rozpad-dle-produktu'!$G$10:$G$18,'Rozpad-dle-produktu'!$C$10:$C$18,"TW")</f>
         <v>96740.0</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>ks / m</t>
         </is>
       </c>
-      <c r="I18" s="7">
+      <c r="J18" s="7">
         <f>SUMIFS('Rozpad-dle-produktu'!$K$10:$K$18,'Rozpad-dle-produktu'!$C$10:$C$18,"TW")</f>
         <v>20506.37</v>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>Ne / No</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>Ne / No — žádné opatření nezjištěno</t>
         </is>
@@ -1005,41 +1029,46 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
+          <t>CI-26051504: 120,00</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
           <t>Tiskové (značkovací) kolečko — není v e-mailu ani v balicím listu, nutno doplnit (viz Poznámky, bod 6)</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Type wheel (printing/marking wheel) — absent from both the forwarder's code list and the packing list; needs identification</t>
         </is>
       </c>
-      <c r="E19" s="10">
+      <c r="F19" s="10">
         <f>SUMIFS('Rozpad-dle-produktu'!$I$10:$I$18,'Rozpad-dle-produktu'!$C$10:$C$18,"OTH")</f>
         <v>0.0</v>
       </c>
-      <c r="F19" s="10">
+      <c r="G19" s="10">
         <f>SUMIFS('Rozpad-dle-produktu'!$J$10:$J$18,'Rozpad-dle-produktu'!$C$10:$C$18,"OTH")</f>
         <v>0.0</v>
       </c>
-      <c r="G19" s="11">
+      <c r="H19" s="11">
         <f>SUMIFS('Rozpad-dle-produktu'!$G$10:$G$18,'Rozpad-dle-produktu'!$C$10:$C$18,"OTH")</f>
         <v>3.0</v>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>ks / pcs</t>
         </is>
       </c>
-      <c r="I19" s="10">
+      <c r="J19" s="10">
         <f>SUMIFS('Rozpad-dle-produktu'!$K$10:$K$18,'Rozpad-dle-produktu'!$C$10:$C$18,"OTH")</f>
         <v>120.0</v>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>Ne / No</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>Ne / No</t>
         </is>
@@ -1049,30 +1078,31 @@
       <c r="A20" s="12" t="n"/>
       <c r="B20" s="12" t="n"/>
       <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>CELKEM / TOTAL</t>
         </is>
-      </c>
-      <c r="E20" s="13">
-        <f>SUM(E16:E19)</f>
-        <v>9643.0</v>
       </c>
       <c r="F20" s="13">
         <f>SUM(F16:F19)</f>
+        <v>9643.0</v>
+      </c>
+      <c r="G20" s="13">
+        <f>SUM(G16:G19)</f>
         <v>11430.0</v>
       </c>
-      <c r="G20" s="14">
-        <f>SUM(G16:G19)</f>
+      <c r="H20" s="14">
+        <f>SUM(H16:H19)</f>
         <v>135208.0</v>
       </c>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="13">
-        <f>SUM(I16:I19)</f>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="13">
+        <f>SUM(J16:J19)</f>
         <v>67063.32</v>
       </c>
-      <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -1087,15 +1117,15 @@
           <t>Hrubá hmotnost vs B/L F202615259</t>
         </is>
       </c>
-      <c r="E23" s="17">
-        <f>F20</f>
+      <c r="F23" s="17">
+        <f>G20</f>
         <v>11430.0</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="G23" s="18" t="n">
         <v>11430</v>
       </c>
-      <c r="G23" s="19" t="str">
-        <f>IF(ROUND(E23-F23,2)=0,"OK","ROZDÍL / DIFF")</f>
+      <c r="H23" s="19" t="str">
+        <f>IF(ROUND(F23-G23,2)=0,"OK","ROZDÍL / DIFF")</f>
         <v>OK</v>
       </c>
     </row>
@@ -1105,15 +1135,15 @@
           <t>Čistá hmotnost vs balicí listy PL-504 + PL-902</t>
         </is>
       </c>
-      <c r="E24" s="17">
-        <f>E20</f>
+      <c r="F24" s="17">
+        <f>F20</f>
         <v>9643.0</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="G24" s="18" t="n">
         <v>9643</v>
       </c>
-      <c r="G24" s="19" t="str">
-        <f>IF(ROUND(E24-F24,2)=0,"OK","ROZDÍL / DIFF")</f>
+      <c r="H24" s="19" t="str">
+        <f>IF(ROUND(F24-G24,2)=0,"OK","ROZDÍL / DIFF")</f>
         <v>OK</v>
       </c>
     </row>
@@ -1123,15 +1153,15 @@
           <t>Celní hodnota vs faktury CI-26051504 + CI-26051902</t>
         </is>
       </c>
-      <c r="E25" s="17">
-        <f>I20</f>
+      <c r="F25" s="17">
+        <f>J20</f>
         <v>67063.32</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="G25" s="18" t="n">
         <v>67063.32000000001</v>
       </c>
-      <c r="G25" s="19" t="str">
-        <f>IF(ROUND(E25-F25,2)=0,"OK","ROZDÍL / DIFF")</f>
+      <c r="H25" s="19" t="str">
+        <f>IF(ROUND(F25-G25,2)=0,"OK","ROZDÍL / DIFF")</f>
         <v>OK</v>
       </c>
     </row>
@@ -1144,20 +1174,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:K9"/>
-    <mergeCell ref="B13:K13"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="B11:K11"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B13:L13"/>
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="B8:L8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/HS_Code_Summary_MOREK_CZ_CZ26008741.xlsx
+++ b/output/HS_Code_Summary_MOREK_CZ_CZ26008741.xlsx
@@ -10010,24 +10010,24 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>3. HS KÓDY NA FAKTURÁCH — prázdné</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>ZJIŠTĚNO</t>
-        </is>
-      </c>
-      <c r="C6" s="41" t="inlineStr">
-        <is>
-          <t>Obě faktury mají sloupec "HS CODE", ale je ve VŠECH řádcích prázdný — dodavatel jej nevyplnil. Klasifikaci jsem proto provedl sám (viz bod 4). Doporučuji vyžádat od dodavatele doplnění.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>3. HS KÓDY NA FAKTURÁCH — doplněny</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>OVĚŘENO</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Původní faktury měly sloupec "HS CODE" prázdný ve všech řádcích. Dodavatel následně vydal REVIDOVANÉ faktury (CI26051504_HScodes, CI26051902_HScodes) s HS kódem u každé položky. Provedl jsem porovnání položku po položce: 97 z 98 řádků má kód vyplněný a VŠECH 97 se shoduje s tímto souhrnem — 8547 20 00 u 32 řádků (HW, MW-A, MW-U), 3917 40 00 u 12 řádků (sady MSTS), 8547 90 00 u 53 řádků (tenkostěnná). Zařazení podle skupin tedy sedí na 100 %. Částky ani množství se na revidovaných fakturách nezměnily (celkem 67 063,32 USD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" s="42" t="inlineStr">
         <is>
           <t>4. POUŽITÉ HS KÓDY — dle speditéra</t>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Souhrn je sestaven podle tří kódů z e-mailu Maurice Ward (L. Jirkovský, ref. OR / MOREK / ASV20260522011 / CZ26008741): 8547 20 00 = smršťovací trubice silnostěnná a středněstěnná (skupiny HW, MW-A, MW-U); 3917 40 00 = spojovací set (skupina KIT — sady MSTS); 8547 90 00 = smršťovací bužírka tenkostěnná (skupina TW). České popisy jsou převzaty doslovně z jeho e-mailu.</t>
+          <t>Souhrn je sestaven podle tří kódů z e-mailu Maurice Ward (L. Jirkovský, ref. OR / MOREK / ASV20260522011 / CZ26008741): 8547 20 00 = smršťovací trubice silnostěnná a středněstěnná (skupiny HW, MW-A, MW-U); 3917 40 00 = spojovací set (skupina KIT — sady MSTS); 8547 90 00 = smršťovací bužírka tenkostěnná (skupina TW). České popisy jsou převzaty doslovně z jeho e-mailu. POTVRZENO: dodavatel mezitím doplnil HS kódy přímo do faktur a u všech 97 zbožových řádků uvádí tytéž tři kódy ve stejném rozdělení (viz bod 3) — speditér a dodavatel se shodují.</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="78" customHeight="1">
+    <row r="12" ht="130" customHeight="1">
       <c r="A12" s="44" t="inlineStr">
         <is>
           <t>6. TYPE WHEEL — 3 ks, chybí všude</t>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Faktura CI-26051504, řádek 78: "type wheel", 3 ks, 40,00 USD/ks = 120,00 USD. Tato položka NENÍ v balicím listu PL-504 (fakturováno 112 548 ks vs. baleno 112 545 ks — rozdíl přesně 3 ks) a NENÍ ani v e-mailu speditéra, který uvádí jen tři kódy pro trubice, bužírky a sety. Nemá tedy žádnou hmotnost a čtvrtý kód pro ni nikdo nestanovil. Podle povahy buď 8442 50 00 (tiskařské typy/štočky), nebo 8443 99 (části tiskáren). Prosím o upřesnění, co to je, zda je fyzicky v zásilce a pod jakým kódem se má deklarovat.</t>
+          <t>Faktura CI-26051504, řádek 78: "type wheel", 3 ks, 40,00 USD/ks = 120,00 USD. Tato položka NENÍ v balicím listu PL-504 (fakturováno 112 548 ks vs. baleno 112 545 ks — rozdíl přesně 3 ks), NENÍ v e-mailu speditéra, a na REVIDOVANÉ faktuře s HS kódy ji dodavatel jako JEDINOU ZE VŠECH 98 řádků nechal BEZ KÓDU. Tři nezávislé zdroje ji tedy vynechávají — to podporuje výklad, že nejde o zasílané zboží, ale o nářadí (tiskové kolečko na potisk trubic), které zůstává u dodavatele. V takovém případě se nedeklaruje samostatně a 120,00 USD se podle čl. 71 odst. 1 písm. b) bodu ii) celního kodexu Unie připočte k celní hodnotě potištěného zboží. Pokud se přesto fyzicky veze, připadá v úvahu 8442 50 00 (tiskařské pomůcky), případně 8443 99 (části tiskových strojů). Podle povahy buď 8442 50 00 (tiskařské typy/štočky), nebo 8443 99 (části tiskáren). Prosím o upřesnění, co to je, zda je fyzicky v zásilce a pod jakým kódem se má deklarovat.</t>
         </is>
       </c>
     </row>
